--- a/exports/BIOCON_full_report.xlsx
+++ b/exports/BIOCON_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>3.17</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.38541666666</v>
+        <v>44579.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>355</v>
+        <v>349.3</v>
       </c>
       <c r="I2" t="n">
         <v>354.018464582215</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.24</v>
+        <v>-1.84</v>
       </c>
       <c r="L2" t="n">
-        <v>0.79</v>
+        <v>2.49</v>
       </c>
       <c r="M2" t="n">
         <v>0.6</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>6.1</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>364.35</v>
+        <v>380</v>
       </c>
       <c r="I3" t="n">
         <v>370.6136030988479</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.31</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>5.77</v>
+        <v>9.49</v>
       </c>
       <c r="M3" t="n">
         <v>1.15</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44613.55208333334</v>
+        <v>44614.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>385.2</v>
+        <v>381.65</v>
       </c>
       <c r="I4" t="n">
         <v>384.795957591214</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K4" t="n">
-        <v>1.37</v>
+        <v>0.43</v>
       </c>
       <c r="L4" t="n">
         <v>6.32</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>5.03</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44644.55208333334</v>
+        <v>44645.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>342</v>
+        <v>348.15</v>
       </c>
       <c r="I5" t="n">
         <v>346.0357689932716</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K5" t="n">
-        <v>10.39</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>4.06</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>5.31</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>350.15</v>
+        <v>340.65</v>
       </c>
       <c r="I6" t="n">
         <v>343.0041780854216</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>0.57</v>
+        <v>-2.15</v>
       </c>
       <c r="L6" t="n">
         <v>3.78</v>
       </c>
       <c r="M6" t="n">
-        <v>0.29</v>
+        <v>0.67</v>
       </c>
       <c r="N6" t="n">
-        <v>1.29</v>
+        <v>2.03</v>
       </c>
       <c r="O6" t="n">
         <v>2.05</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>6.83</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44671.55208333334</v>
+        <v>44672.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>352.6</v>
+        <v>368.7</v>
       </c>
       <c r="I7" t="n">
         <v>360.0743286692779</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.51</v>
+        <v>-8.23</v>
       </c>
       <c r="L7" t="n">
-        <v>3.85</v>
+        <v>8.31</v>
       </c>
       <c r="M7" t="n">
         <v>2.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5.19</v>
+        <v>5.9</v>
       </c>
       <c r="O7" t="n">
         <v>-2.03</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44686.55208333334</v>
+        <v>44687.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>362.55</v>
+        <v>349.55</v>
       </c>
       <c r="I8" t="n">
         <v>357.7825690046517</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.67</v>
+        <v>-5.19</v>
       </c>
       <c r="L8" t="n">
         <v>5.26</v>
@@ -897,7 +992,7 @@
         <v>1.47</v>
       </c>
       <c r="N8" t="n">
-        <v>1.93</v>
+        <v>4.15</v>
       </c>
       <c r="O8" t="n">
         <v>5.9</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44720.55208333334</v>
+        <v>44721.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>321</v>
+        <v>335.75</v>
       </c>
       <c r="I9" t="n">
         <v>332.1336868248274</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K9" t="n">
-        <v>8.17</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
         <v>3.26</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>7.7</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44728.55208333334</v>
+        <v>44729.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>320.5</v>
+        <v>312.6</v>
       </c>
       <c r="I10" t="n">
         <v>318.2237423047009</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.54</v>
+        <v>-6.9</v>
       </c>
       <c r="L10" t="n">
-        <v>5.18</v>
+        <v>7.07</v>
       </c>
       <c r="M10" t="n">
         <v>1.83</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.47</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44750.55208333334</v>
+        <v>44753.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>322.55</v>
+        <v>328.5</v>
       </c>
       <c r="I11" t="n">
         <v>326.5486043959554</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.18</v>
+        <v>-5.09</v>
       </c>
       <c r="L11" t="n">
         <v>8.77</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>5.95</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44767.55208333334</v>
+        <v>44768.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>322.35</v>
+        <v>318.35</v>
       </c>
       <c r="I12" t="n">
         <v>319.4629807708232</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.87</v>
+        <v>-3.09</v>
       </c>
       <c r="L12" t="n">
-        <v>2.77</v>
+        <v>3.68</v>
       </c>
       <c r="M12" t="n">
         <v>0.39</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>5.51</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44817.55208333334</v>
+        <v>44818.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>304</v>
+        <v>307.2</v>
       </c>
       <c r="I13" t="n">
         <v>304.0756687850415</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K13" t="n">
-        <v>4.51</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
         <v>1.92</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>4.78</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>299.4</v>
+        <v>292.8</v>
       </c>
       <c r="I14" t="n">
         <v>295.3339979429488</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.54</v>
+        <v>-4.69</v>
       </c>
       <c r="L14" t="n">
-        <v>3.3</v>
+        <v>4.74</v>
       </c>
       <c r="M14" t="n">
         <v>0.99</v>
       </c>
       <c r="N14" t="n">
-        <v>1.93</v>
+        <v>2.61</v>
       </c>
       <c r="O14" t="n">
         <v>0.43</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.88</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44834.55208333334</v>
+        <v>44837.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>290.3</v>
+        <v>293.25</v>
       </c>
       <c r="I15" t="n">
         <v>292.0227159138175</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K15" t="n">
-        <v>0.85</v>
+        <v>-0.15</v>
       </c>
       <c r="L15" t="n">
         <v>2.83</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>6.24</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44841.55208333334</v>
+        <v>44844.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>282.75</v>
+        <v>277.15</v>
       </c>
       <c r="I16" t="n">
         <v>282.5229042315657</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.58</v>
+        <v>-5.49</v>
       </c>
       <c r="L16" t="n">
-        <v>3.89</v>
+        <v>5.85</v>
       </c>
       <c r="M16" t="n">
-        <v>0.51</v>
+        <v>1.15</v>
       </c>
       <c r="N16" t="n">
         <v>3</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.86</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44859.55208333334</v>
+        <v>44861.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>272.15</v>
+        <v>276.2</v>
       </c>
       <c r="I17" t="n">
         <v>274.0239910668752</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8</v>
+        <v>0.34</v>
       </c>
       <c r="L17" t="n">
         <v>1.06</v>
@@ -1410,7 +1613,7 @@
         <v>0.95</v>
       </c>
       <c r="N17" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="O17" t="n">
         <v>-1.79</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.53</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44901.38541666666</v>
+        <v>44901.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>275.35</v>
+        <v>273.5</v>
       </c>
       <c r="I18" t="n">
         <v>273.569461597951</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.31</v>
+        <v>-0.98</v>
       </c>
       <c r="L18" t="n">
         <v>3.26</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>4.32</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>270.5</v>
+        <v>273.1</v>
       </c>
       <c r="I19" t="n">
         <v>272.1294232660962</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1</v>
+        <v>0.15</v>
       </c>
       <c r="L19" t="n">
         <v>1.65</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>5.2</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44931.55208333334</v>
+        <v>44932.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>260.25</v>
+        <v>255.45</v>
       </c>
       <c r="I20" t="n">
         <v>258.8861976056028</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.71</v>
+        <v>-6.46</v>
       </c>
       <c r="L20" t="n">
-        <v>5.38</v>
+        <v>6.79</v>
       </c>
       <c r="M20" t="n">
         <v>0.04</v>
       </c>
       <c r="N20" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="O20" t="n">
         <v>-0.74</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>4.97</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45019.55208333334</v>
+        <v>45021.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>209</v>
+        <v>215.25</v>
       </c>
       <c r="I21" t="n">
         <v>215.0689379313607</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>87.16666666666667</v>
+        <v>89</v>
       </c>
       <c r="K21" t="n">
-        <v>18.18</v>
+        <v>15.74</v>
       </c>
       <c r="L21" t="n">
         <v>2.35</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.81</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45089.38541666666</v>
+        <v>45089.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>240.05</v>
+        <v>238.95</v>
       </c>
       <c r="I22" t="n">
         <v>239.3464331280391</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>68</v>
+        <v>68.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>11.52</v>
+        <v>11.01</v>
       </c>
       <c r="L22" t="n">
         <v>4</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>4.04</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45105.55208333334</v>
+        <v>45107.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>245.15</v>
+        <v>259.75</v>
       </c>
       <c r="I23" t="n">
         <v>245.7188917596931</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>16</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.59</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>3.75</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>0.51</v>
+        <v>0.59</v>
       </c>
       <c r="N23" t="n">
-        <v>1.77</v>
+        <v>8.1</v>
       </c>
       <c r="O23" t="n">
         <v>-0.79</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>7.01</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45128.55208333334</v>
+        <v>45131.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>264.15</v>
+        <v>250.4</v>
       </c>
       <c r="I24" t="n">
         <v>256.1269070389039</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K24" t="n">
-        <v>1.69</v>
+        <v>-3.6</v>
       </c>
       <c r="L24" t="n">
         <v>5.29</v>
       </c>
       <c r="M24" t="n">
-        <v>0.29</v>
+        <v>1.57</v>
       </c>
       <c r="N24" t="n">
-        <v>2.01</v>
+        <v>5.64</v>
       </c>
       <c r="O24" t="n">
         <v>8.1</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>7.34</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45142.55208333334</v>
+        <v>45145.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>254</v>
+        <v>258.4</v>
       </c>
       <c r="I25" t="n">
         <v>258.1856882463379</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.44</v>
+        <v>-3.19</v>
       </c>
       <c r="L25" t="n">
         <v>4.31</v>
@@ -1866,7 +2165,7 @@
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.92</v>
+        <v>3.94</v>
       </c>
       <c r="O25" t="n">
         <v>-5.64</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>5.3</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45148.55208333334</v>
+        <v>45149.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>261.6</v>
+        <v>258.3</v>
       </c>
       <c r="I26" t="n">
         <v>258.4748274795523</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>1.24</v>
+        <v>-0.04</v>
       </c>
       <c r="L26" t="n">
-        <v>1.97</v>
+        <v>3.37</v>
       </c>
       <c r="M26" t="n">
-        <v>0.24</v>
+        <v>1.78</v>
       </c>
       <c r="N26" t="n">
         <v>2.99</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>7.19</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45174.38541666666</v>
+        <v>45174.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>266.15</v>
+        <v>267.45</v>
       </c>
       <c r="I27" t="n">
         <v>266.9441448929853</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.04</v>
+        <v>-3.54</v>
       </c>
       <c r="L27" t="n">
-        <v>3.72</v>
+        <v>4.26</v>
       </c>
       <c r="M27" t="n">
         <v>0.92</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,25 +2351,25 @@
         <v>4.2</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45190.55208333334</v>
+        <v>45191.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>267.45</v>
+        <v>263.85</v>
       </c>
       <c r="I28" t="n">
         <v>264.0437643276139</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>-1.35</v>
       </c>
       <c r="L28" t="n">
-        <v>0.82</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="N28" t="n">
         <v>3.04</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>6.09</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45198.55208333334</v>
+        <v>45202.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>271.85</v>
+        <v>274.2</v>
       </c>
       <c r="I29" t="n">
         <v>274.0784295915715</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>11</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.03</v>
+        <v>-3.92</v>
       </c>
       <c r="L29" t="n">
-        <v>3.85</v>
+        <v>4.19</v>
       </c>
       <c r="M29" t="n">
         <v>0.88</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>5.49</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45205.55208333334</v>
+        <v>45208.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>264.65</v>
+        <v>260.1</v>
       </c>
       <c r="I30" t="n">
         <v>260.9878678235348</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.48</v>
+        <v>-5.14</v>
       </c>
       <c r="L30" t="n">
-        <v>4.23</v>
+        <v>5.31</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="N30" t="n">
         <v>2.78</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>5.09</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45240.55208333334</v>
+        <v>45242.76041666666</v>
       </c>
       <c r="H31" t="n">
-        <v>228.3</v>
+        <v>235.35</v>
       </c>
       <c r="I31" t="n">
         <v>229.383195051804</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>34.375</v>
       </c>
       <c r="K31" t="n">
-        <v>12.23</v>
+        <v>9.52</v>
       </c>
       <c r="L31" t="n">
         <v>1.44</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>3.37</v>
       </c>
       <c r="N31" t="n">
-        <v>1.35</v>
+        <v>3.09</v>
       </c>
       <c r="O31" t="n">
         <v>-1.66</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.34</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>274</v>
+        <v>266.35</v>
       </c>
       <c r="I32" t="n">
         <v>267.0399507497551</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>68.79166666666667</v>
+        <v>71.625</v>
       </c>
       <c r="K32" t="n">
-        <v>16.42</v>
+        <v>13.17</v>
       </c>
       <c r="L32" t="n">
         <v>4.67</v>
@@ -2265,7 +2648,7 @@
         <v>2.23</v>
       </c>
       <c r="N32" t="n">
-        <v>3.52</v>
+        <v>4.38</v>
       </c>
       <c r="O32" t="n">
         <v>3.09</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45323.55208333334</v>
+        <v>45324.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>269.9</v>
+        <v>277.6</v>
       </c>
       <c r="I33" t="n">
         <v>275.7632421967806</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.33</v>
+        <v>-4.22</v>
       </c>
       <c r="L33" t="n">
-        <v>3.79</v>
+        <v>5.43</v>
       </c>
       <c r="M33" t="n">
         <v>0.8100000000000001</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.06</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45331.38541666666</v>
+        <v>45331.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>275.4</v>
+        <v>274</v>
       </c>
       <c r="I34" t="n">
         <v>275.3240047916171</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.79</v>
+        <v>-1.3</v>
       </c>
       <c r="L34" t="n">
         <v>2.52</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>9.57</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45338.55208333334</v>
+        <v>45341.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>284.55</v>
+        <v>294.4</v>
       </c>
       <c r="I35" t="n">
         <v>293.5352335360759</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.85</v>
+        <v>-7.45</v>
       </c>
       <c r="L35" t="n">
-        <v>5.84</v>
+        <v>10.62</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="N35" t="n">
         <v>3.81</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>270.25</v>
+        <v>260.8</v>
       </c>
       <c r="I36" t="n">
         <v>267.5672932980993</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K36" t="n">
-        <v>-8.199999999999999</v>
+        <v>-11.41</v>
       </c>
       <c r="L36" t="n">
-        <v>9.15</v>
+        <v>12.69</v>
       </c>
       <c r="M36" t="n">
         <v>1.12</v>
       </c>
       <c r="N36" t="n">
-        <v>3.31</v>
+        <v>6.75</v>
       </c>
       <c r="O36" t="n">
         <v>1.92</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>10.34</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>264.2</v>
+        <v>271.15</v>
       </c>
       <c r="I37" t="n">
         <v>267.2918666242938</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.3</v>
+        <v>-3.97</v>
       </c>
       <c r="L37" t="n">
         <v>4.85</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.46</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45401.38541666666</v>
+        <v>45401.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>264.4</v>
+        <v>261.2</v>
       </c>
       <c r="I38" t="n">
         <v>263.6838773995413</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.49</v>
+        <v>-3.67</v>
       </c>
       <c r="L38" t="n">
         <v>4.17</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>7.92</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45405.55208333334</v>
+        <v>45406.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>280.35</v>
+        <v>293.8</v>
       </c>
       <c r="I39" t="n">
         <v>281.8996222515908</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>-7.33</v>
+        <v>-12.48</v>
       </c>
       <c r="L39" t="n">
-        <v>7.58</v>
+        <v>12.94</v>
       </c>
       <c r="M39" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="N39" t="n">
         <v>4</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>310.5</v>
+        <v>289.5</v>
       </c>
       <c r="I40" t="n">
         <v>301.1284335472403</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K40" t="n">
-        <v>5.68</v>
+        <v>-1.46</v>
       </c>
       <c r="L40" t="n">
-        <v>4.22</v>
+        <v>8.25</v>
       </c>
       <c r="M40" t="n">
         <v>1.21</v>
       </c>
       <c r="N40" t="n">
-        <v>3.26</v>
+        <v>5.97</v>
       </c>
       <c r="O40" t="n">
         <v>3.09</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>11.24</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45449.38541666666</v>
+        <v>45449.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>316.05</v>
+        <v>335.75</v>
       </c>
       <c r="I41" t="n">
         <v>322.0438765741976</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-9.17</v>
+        <v>-15.98</v>
       </c>
       <c r="L41" t="n">
-        <v>11.66</v>
+        <v>15.98</v>
       </c>
       <c r="M41" t="n">
         <v>0.98</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>14.13</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45484.55208333334</v>
+        <v>45485.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>355.25</v>
+        <v>350.3</v>
       </c>
       <c r="I42" t="n">
         <v>350.3455098083278</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K42" t="n">
-        <v>5.81</v>
+        <v>4.33</v>
       </c>
       <c r="L42" t="n">
         <v>6.34</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.4</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45497.55208333334</v>
+        <v>45498.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>347.5</v>
+        <v>359.45</v>
       </c>
       <c r="I43" t="n">
         <v>353.1447020926016</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8</v>
+        <v>-2.61</v>
       </c>
       <c r="L43" t="n">
         <v>3.2</v>
@@ -2892,7 +3407,7 @@
         <v>0.7</v>
       </c>
       <c r="N43" t="n">
-        <v>3.12</v>
+        <v>4.46</v>
       </c>
       <c r="O43" t="n">
         <v>-1.34</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>356</v>
+        <v>339.8</v>
       </c>
       <c r="I44" t="n">
         <v>342.5465525002058</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.96</v>
+        <v>-5.47</v>
       </c>
       <c r="L44" t="n">
-        <v>4.76</v>
+        <v>7.16</v>
       </c>
       <c r="M44" t="n">
-        <v>1.55</v>
+        <v>3.36</v>
       </c>
       <c r="N44" t="n">
-        <v>1.79</v>
+        <v>5.1</v>
       </c>
       <c r="O44" t="n">
         <v>4.46</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45525.38541666666</v>
+        <v>45525.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>352.1</v>
+        <v>356</v>
       </c>
       <c r="I45" t="n">
         <v>353.9347729797882</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.62</v>
+        <v>-4.77</v>
       </c>
       <c r="L45" t="n">
-        <v>4.13</v>
+        <v>4.9</v>
       </c>
       <c r="M45" t="n">
         <v>2.2</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.62</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45552.55208333334</v>
+        <v>45553.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>375.25</v>
+        <v>362</v>
       </c>
       <c r="I46" t="n">
         <v>364.9965115791413</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>5.41</v>
+        <v>1.69</v>
       </c>
       <c r="L46" t="n">
         <v>1.67</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>10.32</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45604.55208333334</v>
+        <v>45607.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>320.6</v>
+        <v>347.35</v>
       </c>
       <c r="I47" t="n">
         <v>334.2102490428127</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K47" t="n">
-        <v>11.44</v>
+        <v>4.05</v>
       </c>
       <c r="L47" t="n">
         <v>5.47</v>
       </c>
       <c r="M47" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="N47" t="n">
-        <v>2.96</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O47" t="n">
         <v>-3.33</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>10.65</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45615.55208333334</v>
+        <v>45617.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>325.2</v>
+        <v>324.9</v>
       </c>
       <c r="I48" t="n">
         <v>325.1342310430001</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.38</v>
+        <v>-6.46</v>
       </c>
       <c r="L48" t="n">
-        <v>6.52</v>
+        <v>8.02</v>
       </c>
       <c r="M48" t="n">
         <v>0.35</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>7.4</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45622.38541666666</v>
+        <v>45622.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>344.75</v>
+        <v>352.3</v>
       </c>
       <c r="I49" t="n">
         <v>347.7400404324224</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K49" t="n">
-        <v>-6.11</v>
+        <v>-8.43</v>
       </c>
       <c r="L49" t="n">
-        <v>6.16</v>
+        <v>9.4</v>
       </c>
       <c r="M49" t="n">
         <v>1.03</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.02</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45637.55208333334</v>
+        <v>45638.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>367</v>
+        <v>357.3</v>
       </c>
       <c r="I50" t="n">
         <v>359.2004065361693</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>4.17</v>
+        <v>1.42</v>
       </c>
       <c r="L50" t="n">
         <v>2.17</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.55</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45652.55208333334</v>
+        <v>45653.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>347.45</v>
+        <v>352.95</v>
       </c>
       <c r="I51" t="n">
         <v>350.2524883259098</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K51" t="n">
-        <v>2.76</v>
+        <v>1.22</v>
       </c>
       <c r="L51" t="n">
         <v>3.37</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.6</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45684.38541666666</v>
+        <v>45684.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>373.45</v>
+        <v>371.4</v>
       </c>
       <c r="I52" t="n">
         <v>372.8450151385663</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>5.81</v>
+        <v>5.23</v>
       </c>
       <c r="L52" t="n">
         <v>1.84</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>7.4</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45692.55208333334</v>
+        <v>45693.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>370.4</v>
+        <v>391.75</v>
       </c>
       <c r="I53" t="n">
         <v>385.2447086239304</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K53" t="n">
-        <v>0.27</v>
+        <v>-5.48</v>
       </c>
       <c r="L53" t="n">
-        <v>1.14</v>
+        <v>6.02</v>
       </c>
       <c r="M53" t="n">
         <v>0.82</v>
       </c>
       <c r="N53" t="n">
-        <v>2.57</v>
+        <v>5.36</v>
       </c>
       <c r="O53" t="n">
         <v>-4.39</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>10.68</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>377.4</v>
+        <v>361.15</v>
       </c>
       <c r="I54" t="n">
         <v>365.9869064653942</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.66</v>
+        <v>-7.81</v>
       </c>
       <c r="L54" t="n">
-        <v>5.18</v>
+        <v>7.94</v>
       </c>
       <c r="M54" t="n">
         <v>0.3</v>
       </c>
       <c r="N54" t="n">
-        <v>2.99</v>
+        <v>4.08</v>
       </c>
       <c r="O54" t="n">
         <v>5.36</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>10.78</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>324.5</v>
+        <v>328.6</v>
       </c>
       <c r="I55" t="n">
         <v>325.9506822730846</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K55" t="n">
-        <v>10.15</v>
+        <v>9.01</v>
       </c>
       <c r="L55" t="n">
         <v>4.86</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>8.17</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>345.9</v>
+        <v>328.5</v>
       </c>
       <c r="I56" t="n">
         <v>334.3656654551025</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K56" t="n">
-        <v>5.26</v>
+        <v>-0.03</v>
       </c>
       <c r="L56" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="M56" t="n">
-        <v>0.7</v>
+        <v>0.97</v>
       </c>
       <c r="N56" t="n">
-        <v>1.67</v>
+        <v>5.17</v>
       </c>
       <c r="O56" t="n">
         <v>2</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>9.06</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45769.55208333334</v>
+        <v>45770.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>334</v>
+        <v>336.7</v>
       </c>
       <c r="I57" t="n">
         <v>335.8946644757764</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.67</v>
+        <v>-2.5</v>
       </c>
       <c r="L57" t="n">
         <v>4.47</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>6.31</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45771.55208333334</v>
+        <v>45772.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>325.75</v>
+        <v>313.95</v>
       </c>
       <c r="I58" t="n">
         <v>316.9156005246319</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.25</v>
+        <v>-6.76</v>
       </c>
       <c r="L58" t="n">
-        <v>3.46</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M58" t="n">
         <v>0.45</v>
       </c>
       <c r="N58" t="n">
-        <v>2.91</v>
+        <v>4.22</v>
       </c>
       <c r="O58" t="n">
         <v>0.45</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>8.91</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45782.38541666666</v>
+        <v>45782.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>333.65</v>
+        <v>336</v>
       </c>
       <c r="I59" t="n">
         <v>334.836356995789</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.27</v>
+        <v>-7.02</v>
       </c>
       <c r="L59" t="n">
-        <v>6.66</v>
+        <v>7.28</v>
       </c>
       <c r="M59" t="n">
         <v>1.13</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.46</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45873.38541666666</v>
+        <v>45873.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>383.55</v>
+        <v>381.45</v>
       </c>
       <c r="I60" t="n">
         <v>381.9293585800136</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>90.83333333333333</v>
+        <v>91</v>
       </c>
       <c r="K60" t="n">
-        <v>14.15</v>
+        <v>13.53</v>
       </c>
       <c r="L60" t="n">
         <v>5.39</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>6.07</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45905.55208333334</v>
+        <v>45908.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>363.4</v>
+        <v>366</v>
       </c>
       <c r="I61" t="n">
         <v>365.2477130101094</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>32</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K61" t="n">
-        <v>4.73</v>
+        <v>4.05</v>
       </c>
       <c r="L61" t="n">
         <v>1.4</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>4.95</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45925.38541666666</v>
+        <v>45925.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>356.8</v>
+        <v>354.75</v>
       </c>
       <c r="I62" t="n">
         <v>355.3259459588915</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.51</v>
+        <v>-3.07</v>
       </c>
       <c r="L62" t="n">
         <v>3.55</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>4.71</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45945.38541666666</v>
+        <v>45945.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>355.1</v>
+        <v>356.1</v>
       </c>
       <c r="I63" t="n">
         <v>355.6431480393493</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.1</v>
+        <v>-0.38</v>
       </c>
       <c r="L63" t="n">
         <v>1.09</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>4.86</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45980.55208333334</v>
+        <v>45981.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>409.8</v>
+        <v>394.95</v>
       </c>
       <c r="I64" t="n">
         <v>398.2935235920579</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K64" t="n">
-        <v>15.08</v>
+        <v>10.91</v>
       </c>
       <c r="L64" t="n">
         <v>0.65</v>
@@ -4089,7 +4856,7 @@
         <v>0.53</v>
       </c>
       <c r="N64" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="O64" t="n">
         <v>1.51</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>398.2</v>
+        <v>401.55</v>
       </c>
       <c r="I65" t="n">
         <v>400.0825287605904</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.82</v>
+        <v>-1.67</v>
       </c>
       <c r="L65" t="n">
         <v>4.44</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>4.7</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46028.38541666666</v>
+        <v>46028.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>389.45</v>
+        <v>386.45</v>
       </c>
       <c r="I66" t="n">
         <v>386.7866031381096</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.01</v>
+        <v>-3.76</v>
       </c>
       <c r="L66" t="n">
-        <v>3.85</v>
+        <v>4.63</v>
       </c>
       <c r="M66" t="n">
         <v>0.46</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>4.16</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46071.55208333334</v>
+        <v>46072.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>378.65</v>
+        <v>386.65</v>
       </c>
       <c r="I67" t="n">
         <v>383.2623877054559</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>43</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="K67" t="n">
-        <v>2.02</v>
+        <v>-0.05</v>
       </c>
       <c r="L67" t="n">
         <v>1.84</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>6.31</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46094.55208333334</v>
+        <v>46097.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>385</v>
+        <v>369.35</v>
       </c>
       <c r="I68" t="n">
         <v>377.4549619070074</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.43</v>
+        <v>-4.47</v>
       </c>
       <c r="L68" t="n">
-        <v>2.92</v>
+        <v>4.54</v>
       </c>
       <c r="M68" t="n">
         <v>2.5</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>9.66</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46140.55208333334</v>
+        <v>46141.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>363.55</v>
+        <v>364.95</v>
       </c>
       <c r="I69" t="n">
         <v>364.1025127038096</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K69" t="n">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="L69" t="n">
         <v>5.02</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>4.41</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46174.55208333334</v>
+        <v>46175.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>427</v>
+        <v>414.4</v>
       </c>
       <c r="I70" t="n">
         <v>415.8610373550305</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K70" t="n">
-        <v>17</v>
+        <v>13.55</v>
       </c>
       <c r="L70" t="n">
         <v>2.93</v>
@@ -4431,7 +5270,7 @@
         <v>1.17</v>
       </c>
       <c r="N70" t="n">
-        <v>1.25</v>
+        <v>2.46</v>
       </c>
       <c r="O70" t="n">
         <v>-0.11</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>6.73</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46216.55208333334</v>
+        <v>46217.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>413.8</v>
+        <v>436</v>
       </c>
       <c r="I71" t="n">
         <v>423.0996064917181</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K71" t="n">
-        <v>0.14</v>
+        <v>-5.21</v>
       </c>
       <c r="L71" t="n">
-        <v>4.28</v>
+        <v>7.26</v>
       </c>
       <c r="M71" t="n">
-        <v>1.14</v>
+        <v>3.27</v>
       </c>
       <c r="N71" t="n">
-        <v>2.9</v>
+        <v>5.61</v>
       </c>
       <c r="O71" t="n">
         <v>-2.46</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>8.81</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46247.55208333334</v>
+        <v>46248.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>420</v>
+        <v>416.75</v>
       </c>
       <c r="I72" t="n">
         <v>417.3818706885017</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K72" t="n">
-        <v>-3.67</v>
+        <v>-4.42</v>
       </c>
       <c r="L72" t="n">
-        <v>4.54</v>
+        <v>4.83</v>
       </c>
       <c r="M72" t="n">
         <v>1.59</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>4.75</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46286.38541666666</v>
+        <v>46286.55208333334</v>
       </c>
       <c r="H73" t="n">
-        <v>394.3</v>
+        <v>395.15</v>
       </c>
       <c r="I73" t="n">
         <v>394.5011545047111</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K73" t="n">
-        <v>5.39</v>
+        <v>5.18</v>
       </c>
       <c r="L73" t="n">
         <v>1.16</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>4.37</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46290.55208333334</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>381</v>
+        <v>377.1</v>
       </c>
       <c r="I74" t="n">
         <v>379.6076452980408</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.58</v>
+        <v>-4.57</v>
       </c>
       <c r="L74" t="n">
-        <v>3.71</v>
+        <v>5.07</v>
       </c>
       <c r="M74" t="n">
         <v>0.91</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4719,6 +5618,14 @@
       <c r="Q75" t="n">
         <v>40</v>
       </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6821,7 +7728,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.3</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="6">
@@ -6831,7 +7738,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="7">
@@ -6841,7 +7748,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>90.8</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
@@ -6851,7 +7758,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6861,7 +7768,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -6871,7 +7778,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42.6</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="11">
@@ -6881,7 +7788,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -6891,7 +7798,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -6901,7 +7808,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69.90000000000001</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="14">
@@ -6911,7 +7818,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.14</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="15">
@@ -6921,7 +7828,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.33</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="16">
@@ -6931,7 +7838,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9399999999999999</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="17">
@@ -6941,7 +7848,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18.18</v>
+        <v>15.98</v>
       </c>
     </row>
     <row r="18">
@@ -6951,7 +7858,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.2</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="19">
@@ -6961,7 +7868,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.94</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="20">
@@ -6971,7 +7878,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.85</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="21">
@@ -6981,7 +7888,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.66</v>
+        <v>15.98</v>
       </c>
     </row>
     <row r="22">
@@ -6991,7 +7898,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -7001,7 +7908,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -7011,7 +7918,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="25">
@@ -7031,7 +7938,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.11</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="27">
@@ -7051,7 +7958,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
